--- a/forest_fires.xlsx
+++ b/forest_fires.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eylulezgiozer/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eylulezgiozer/Documents/GitHub/emu430-fall2024-team-dataflame/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C75F407-C7F3-7645-891F-CE76C12D519A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10B683A-817F-5444-978F-BC2D8696CD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="920" windowWidth="28240" windowHeight="16940" xr2:uid="{3895F9BE-A707-964F-8BA2-144EDD3563A5}"/>
+    <workbookView xWindow="0" yWindow="1000" windowWidth="28240" windowHeight="16940" xr2:uid="{3895F9BE-A707-964F-8BA2-144EDD3563A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -39,22 +39,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Year </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="12">
   <si>
     <t>Burned_area</t>
   </si>
   <si>
     <t>Number_of_fires</t>
   </si>
+  <si>
+    <t xml:space="preserve">Year </t>
+  </si>
+  <si>
+    <t>Intentional_number</t>
+  </si>
+  <si>
+    <t>Intentional_hectare</t>
+  </si>
+  <si>
+    <t>Negligence_number</t>
+  </si>
+  <si>
+    <t>Negligence_hectare</t>
+  </si>
+  <si>
+    <t>Natural_number</t>
+  </si>
+  <si>
+    <t>Natural_hecatre</t>
+  </si>
+  <si>
+    <t>Unknown_number</t>
+  </si>
+  <si>
+    <t>Unknown_hectare</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00;[Red]0.00"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -70,28 +100,46 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -99,15 +147,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,481 +522,1468 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03995E79-A56B-3C44-B1D4-715E266F2AAE}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="29.1640625" customWidth="1"/>
+    <col min="13" max="13" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
         <v>1988</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="5">
         <v>18210</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="6">
         <v>1372</v>
       </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
+      <c r="D2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
         <v>1989</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="5">
         <v>13099</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="6">
         <v>1633</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
         <v>1990</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="5">
         <v>13742</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="6">
         <v>1750</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+      <c r="D4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
         <v>1991</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <v>8081</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="6">
         <v>1481</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+      <c r="D5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
         <v>1992</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>12232</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="6">
         <v>2117</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="D6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
         <v>1993</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="5">
         <v>15393</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="6">
         <v>2545</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
         <v>1994</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <v>30828</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="6">
         <v>3239</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+      <c r="D8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
         <v>1995</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <v>7676</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="6">
         <v>1770</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="D9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>1996</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <v>14922</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="6">
         <v>1645</v>
       </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+      <c r="D10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
         <v>1997</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="5">
         <v>6317</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="6">
         <v>1339</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="D11" s="7">
+        <v>193</v>
+      </c>
+      <c r="E11" s="7">
+        <v>923</v>
+      </c>
+      <c r="F11" s="7">
+        <v>696</v>
+      </c>
+      <c r="G11" s="7">
+        <v>3389</v>
+      </c>
+      <c r="H11" s="7">
+        <v>78</v>
+      </c>
+      <c r="I11" s="7">
+        <v>37</v>
+      </c>
+      <c r="J11" s="7">
+        <v>372</v>
+      </c>
+      <c r="K11" s="7">
+        <v>1968</v>
+      </c>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>1998</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>6764</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="6">
         <v>1932</v>
       </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
+      <c r="D12" s="7">
+        <v>249</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1655</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1163</v>
+      </c>
+      <c r="G12" s="7">
+        <v>3713</v>
+      </c>
+      <c r="H12" s="7">
+        <v>53</v>
+      </c>
+      <c r="I12" s="7">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7">
+        <v>467</v>
+      </c>
+      <c r="K12" s="7">
+        <v>1376</v>
+      </c>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
         <v>1999</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="5">
         <v>5804</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="6">
         <v>2075</v>
       </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
+      <c r="D13" s="7">
+        <v>279</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1926</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1151</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2808</v>
+      </c>
+      <c r="H13" s="7">
+        <v>203</v>
+      </c>
+      <c r="I13" s="7">
+        <v>126</v>
+      </c>
+      <c r="J13" s="7">
+        <v>442</v>
+      </c>
+      <c r="K13" s="7">
+        <v>944</v>
+      </c>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>2000</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>26353</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="6">
         <v>2353</v>
       </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
+      <c r="D14" s="7">
+        <v>410</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4417</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1384</v>
+      </c>
+      <c r="G14" s="7">
+        <v>19017</v>
+      </c>
+      <c r="H14" s="7">
+        <v>132</v>
+      </c>
+      <c r="I14" s="7">
+        <v>167</v>
+      </c>
+      <c r="J14" s="7">
+        <v>427</v>
+      </c>
+      <c r="K14" s="7">
+        <v>2752</v>
+      </c>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
         <v>2001</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="5">
         <v>7394</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="6">
         <v>2631</v>
       </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
+      <c r="D15" s="7">
+        <v>251</v>
+      </c>
+      <c r="E15" s="7">
+        <v>651</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1629</v>
+      </c>
+      <c r="G15" s="7">
+        <v>4247</v>
+      </c>
+      <c r="H15" s="7">
+        <v>188</v>
+      </c>
+      <c r="I15" s="7">
+        <v>735</v>
+      </c>
+      <c r="J15" s="7">
+        <v>563</v>
+      </c>
+      <c r="K15" s="7">
+        <v>1761</v>
+      </c>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
         <v>2002</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="5">
         <v>8514</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="6">
         <v>1471</v>
       </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
+      <c r="D16" s="7">
+        <v>218</v>
+      </c>
+      <c r="E16" s="7">
+        <v>509</v>
+      </c>
+      <c r="F16" s="7">
+        <v>809</v>
+      </c>
+      <c r="G16" s="7">
+        <v>7287</v>
+      </c>
+      <c r="H16" s="7">
+        <v>181</v>
+      </c>
+      <c r="I16" s="7">
+        <v>261</v>
+      </c>
+      <c r="J16" s="7">
+        <v>263</v>
+      </c>
+      <c r="K16" s="7">
+        <v>457</v>
+      </c>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
         <v>2003</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="5">
         <v>6644</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="6">
         <v>2177</v>
       </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
+      <c r="D17" s="7">
+        <v>258</v>
+      </c>
+      <c r="E17" s="7">
+        <v>665</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1317</v>
+      </c>
+      <c r="G17" s="7">
+        <v>4520</v>
+      </c>
+      <c r="H17" s="7">
+        <v>120</v>
+      </c>
+      <c r="I17" s="7">
+        <v>694</v>
+      </c>
+      <c r="J17" s="7">
+        <v>482</v>
+      </c>
+      <c r="K17" s="7">
+        <v>765</v>
+      </c>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
         <v>2004</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="5">
         <v>4876.2</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="6">
         <v>1762</v>
       </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
+      <c r="D18" s="7">
+        <v>242</v>
+      </c>
+      <c r="E18" s="7">
+        <v>748.4</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1033</v>
+      </c>
+      <c r="G18" s="7">
+        <v>3093</v>
+      </c>
+      <c r="H18" s="7">
+        <v>128</v>
+      </c>
+      <c r="I18" s="7">
+        <v>232.5</v>
+      </c>
+      <c r="J18" s="7">
+        <v>359</v>
+      </c>
+      <c r="K18" s="7">
+        <v>802.3</v>
+      </c>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
         <v>2005</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="5">
         <v>2821</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="6">
         <v>1530</v>
       </c>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
+      <c r="D19" s="7">
+        <v>272</v>
+      </c>
+      <c r="E19" s="7">
+        <v>401.7</v>
+      </c>
+      <c r="F19" s="7">
+        <v>867</v>
+      </c>
+      <c r="G19" s="7">
+        <v>2084</v>
+      </c>
+      <c r="H19" s="7">
+        <v>140</v>
+      </c>
+      <c r="I19" s="7">
+        <v>47.5</v>
+      </c>
+      <c r="J19" s="7">
+        <v>251</v>
+      </c>
+      <c r="K19" s="7">
+        <v>287.8</v>
+      </c>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
         <v>2006</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="5">
         <v>7761.6</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
         <v>2227</v>
       </c>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
+      <c r="D20" s="7">
+        <v>166</v>
+      </c>
+      <c r="E20" s="7">
+        <v>206.2</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1315</v>
+      </c>
+      <c r="G20" s="7">
+        <v>5873</v>
+      </c>
+      <c r="H20" s="7">
+        <v>330</v>
+      </c>
+      <c r="I20" s="7">
+        <v>543</v>
+      </c>
+      <c r="J20" s="7">
+        <v>416</v>
+      </c>
+      <c r="K20" s="7">
+        <v>1139.4000000000001</v>
+      </c>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
         <v>2007</v>
       </c>
-      <c r="B21" s="3">
-        <v>11664.4</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="B21" s="5">
+        <v>11664.400000000001</v>
+      </c>
+      <c r="C21" s="6">
         <v>2829</v>
       </c>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
+      <c r="D21" s="7">
+        <v>292</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1705.1</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1642</v>
+      </c>
+      <c r="G21" s="7">
+        <v>7994</v>
+      </c>
+      <c r="H21" s="7">
+        <v>407</v>
+      </c>
+      <c r="I21" s="7">
+        <v>243.2</v>
+      </c>
+      <c r="J21" s="7">
+        <v>488</v>
+      </c>
+      <c r="K21" s="7">
+        <v>1722.1</v>
+      </c>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
         <v>2008</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="5">
         <v>29749</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="6">
         <v>2135</v>
       </c>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
+      <c r="D22" s="7">
+        <v>377</v>
+      </c>
+      <c r="E22" s="7">
+        <v>797</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1018</v>
+      </c>
+      <c r="G22" s="7">
+        <v>26283</v>
+      </c>
+      <c r="H22" s="7">
+        <v>330</v>
+      </c>
+      <c r="I22" s="7">
+        <v>699</v>
+      </c>
+      <c r="J22" s="7">
+        <v>410</v>
+      </c>
+      <c r="K22" s="7">
+        <v>1970</v>
+      </c>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
         <v>2009</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="5">
         <v>4679</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="6">
         <v>1793</v>
       </c>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
+      <c r="D23" s="7">
+        <v>231</v>
+      </c>
+      <c r="E23" s="7">
+        <v>792</v>
+      </c>
+      <c r="F23" s="7">
+        <v>884</v>
+      </c>
+      <c r="G23" s="7">
+        <v>3082</v>
+      </c>
+      <c r="H23" s="7">
+        <v>333</v>
+      </c>
+      <c r="I23" s="7">
+        <v>105</v>
+      </c>
+      <c r="J23" s="7">
+        <v>345</v>
+      </c>
+      <c r="K23" s="7">
+        <v>700</v>
+      </c>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
         <v>2010</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="5">
         <v>3317</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="6">
         <v>1861</v>
       </c>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
+      <c r="D24" s="7">
+        <v>146</v>
+      </c>
+      <c r="E24" s="7">
+        <v>526</v>
+      </c>
+      <c r="F24" s="7">
+        <v>861</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1851</v>
+      </c>
+      <c r="H24" s="7">
+        <v>281</v>
+      </c>
+      <c r="I24" s="7">
+        <v>69</v>
+      </c>
+      <c r="J24" s="7">
+        <v>573</v>
+      </c>
+      <c r="K24" s="7">
+        <v>871</v>
+      </c>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
         <v>2011</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="5">
         <v>3612</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="6">
         <v>1954</v>
       </c>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
+      <c r="D25" s="7">
+        <v>153</v>
+      </c>
+      <c r="E25" s="7">
+        <v>283</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1067</v>
+      </c>
+      <c r="G25" s="7">
+        <v>2368</v>
+      </c>
+      <c r="H25" s="7">
+        <v>130</v>
+      </c>
+      <c r="I25" s="7">
+        <v>39</v>
+      </c>
+      <c r="J25" s="7">
+        <v>604</v>
+      </c>
+      <c r="K25" s="7">
+        <v>922</v>
+      </c>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
         <v>2012</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="8">
         <v>10454</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="6">
         <v>2450</v>
       </c>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
+      <c r="D26" s="7">
+        <v>197</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1615</v>
+      </c>
+      <c r="F26" s="7">
+        <v>936</v>
+      </c>
+      <c r="G26" s="7">
+        <v>5780</v>
+      </c>
+      <c r="H26" s="7">
+        <v>373</v>
+      </c>
+      <c r="I26" s="7">
+        <v>334</v>
+      </c>
+      <c r="J26" s="7">
+        <v>944</v>
+      </c>
+      <c r="K26" s="7">
+        <v>2725</v>
+      </c>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
         <v>2013</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="8">
         <v>11456</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="6">
         <v>3755</v>
       </c>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
+      <c r="D27" s="7">
+        <v>260</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1478.48</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1419</v>
+      </c>
+      <c r="G27" s="7">
+        <v>4051</v>
+      </c>
+      <c r="H27" s="7">
+        <v>258</v>
+      </c>
+      <c r="I27" s="7">
+        <v>138</v>
+      </c>
+      <c r="J27" s="7">
+        <v>1818</v>
+      </c>
+      <c r="K27" s="7">
+        <v>5789</v>
+      </c>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
         <v>2014</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="8">
         <v>3117</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="6">
         <v>2149</v>
       </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
+      <c r="D28" s="7">
+        <v>127</v>
+      </c>
+      <c r="E28" s="7">
+        <v>85</v>
+      </c>
+      <c r="F28" s="7">
+        <v>801</v>
+      </c>
+      <c r="G28" s="7">
+        <v>1682</v>
+      </c>
+      <c r="H28" s="7">
+        <v>328</v>
+      </c>
+      <c r="I28" s="7">
+        <v>77</v>
+      </c>
+      <c r="J28" s="7">
+        <v>893</v>
+      </c>
+      <c r="K28" s="7">
+        <v>1273</v>
+      </c>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="9">
         <v>2015</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="10">
         <v>3219</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="6">
         <v>2150</v>
       </c>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
+      <c r="D29" s="7">
+        <v>138</v>
+      </c>
+      <c r="E29" s="7">
+        <v>167</v>
+      </c>
+      <c r="F29" s="7">
+        <v>794</v>
+      </c>
+      <c r="G29" s="7">
+        <v>1198</v>
+      </c>
+      <c r="H29" s="7">
+        <v>257</v>
+      </c>
+      <c r="I29" s="7">
+        <v>95</v>
+      </c>
+      <c r="J29" s="7">
+        <v>961</v>
+      </c>
+      <c r="K29" s="7">
+        <v>1759</v>
+      </c>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
         <v>2016</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="11">
         <v>9156</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="6">
         <v>3188</v>
       </c>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
+      <c r="D30" s="7">
+        <v>157</v>
+      </c>
+      <c r="E30" s="7">
+        <v>240</v>
+      </c>
+      <c r="F30" s="7">
+        <v>990</v>
+      </c>
+      <c r="G30" s="7">
+        <v>5222</v>
+      </c>
+      <c r="H30" s="7">
+        <v>310</v>
+      </c>
+      <c r="I30" s="7">
+        <v>170</v>
+      </c>
+      <c r="J30" s="7">
+        <v>1731</v>
+      </c>
+      <c r="K30" s="7">
+        <v>3524</v>
+      </c>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
         <v>2017</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="5">
         <v>11993</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="6">
         <v>2411</v>
       </c>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
+      <c r="D31" s="7">
+        <v>151</v>
+      </c>
+      <c r="E31" s="7">
+        <v>619</v>
+      </c>
+      <c r="F31" s="7">
+        <v>721</v>
+      </c>
+      <c r="G31" s="7">
+        <v>7146</v>
+      </c>
+      <c r="H31" s="7">
+        <v>259</v>
+      </c>
+      <c r="I31" s="7">
+        <v>84</v>
+      </c>
+      <c r="J31" s="7">
+        <v>1280</v>
+      </c>
+      <c r="K31" s="7">
+        <v>4144</v>
+      </c>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
         <v>2018</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="5">
         <v>5644</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="6">
         <v>2167</v>
       </c>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
+      <c r="D32" s="7">
+        <v>92</v>
+      </c>
+      <c r="E32" s="7">
+        <v>148</v>
+      </c>
+      <c r="F32" s="7">
+        <v>693</v>
+      </c>
+      <c r="G32" s="7">
+        <v>2216</v>
+      </c>
+      <c r="H32" s="7">
+        <v>413</v>
+      </c>
+      <c r="I32" s="7">
+        <v>141</v>
+      </c>
+      <c r="J32" s="7">
+        <v>969</v>
+      </c>
+      <c r="K32" s="7">
+        <v>3139</v>
+      </c>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="12">
         <v>2019</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="11">
         <v>11332</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="6">
         <v>2688</v>
       </c>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
+      <c r="D33" s="7">
+        <v>124</v>
+      </c>
+      <c r="E33" s="7">
+        <v>686</v>
+      </c>
+      <c r="F33" s="7">
+        <v>883</v>
+      </c>
+      <c r="G33" s="7">
+        <v>6529</v>
+      </c>
+      <c r="H33" s="7">
+        <v>372</v>
+      </c>
+      <c r="I33" s="7">
+        <v>373</v>
+      </c>
+      <c r="J33" s="7">
+        <v>1309</v>
+      </c>
+      <c r="K33" s="7">
+        <v>3744</v>
+      </c>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
         <v>2020</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="11">
         <v>20971</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="6">
         <v>3399</v>
       </c>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
+      <c r="D34" s="7">
+        <v>72</v>
+      </c>
+      <c r="E34" s="7">
+        <v>718</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1156</v>
+      </c>
+      <c r="G34" s="7">
+        <v>8285</v>
+      </c>
+      <c r="H34" s="7">
+        <v>312</v>
+      </c>
+      <c r="I34" s="7">
+        <v>197</v>
+      </c>
+      <c r="J34" s="7">
+        <v>1859</v>
+      </c>
+      <c r="K34" s="7">
+        <v>11771</v>
+      </c>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="12">
         <v>2021</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="11">
         <v>139503</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="6">
         <v>2793</v>
       </c>
-      <c r="D35" s="1"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
+      <c r="D35" s="7">
+        <v>110</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46147</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1001</v>
+      </c>
+      <c r="G35" s="7">
+        <v>46879</v>
+      </c>
+      <c r="H35" s="7">
+        <v>353</v>
+      </c>
+      <c r="I35" s="7">
+        <v>208</v>
+      </c>
+      <c r="J35" s="7">
+        <v>1329</v>
+      </c>
+      <c r="K35" s="7">
+        <v>46269</v>
+      </c>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="12">
         <v>2022</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="11">
         <v>12799</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="6">
         <v>2160</v>
       </c>
-      <c r="D36" s="1"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
+      <c r="D36" s="7">
+        <v>86</v>
+      </c>
+      <c r="E36" s="7">
+        <v>4722</v>
+      </c>
+      <c r="F36" s="7">
+        <v>830</v>
+      </c>
+      <c r="G36" s="7">
+        <v>5428</v>
+      </c>
+      <c r="H36" s="7">
+        <v>358</v>
+      </c>
+      <c r="I36" s="7">
+        <v>517</v>
+      </c>
+      <c r="J36" s="7">
+        <v>886</v>
+      </c>
+      <c r="K36" s="7">
+        <v>2132</v>
+      </c>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
         <v>2023</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="11">
         <v>15520</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="6">
         <v>2579</v>
       </c>
-      <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
+      <c r="D37" s="7">
+        <v>92</v>
+      </c>
+      <c r="E37" s="7">
+        <v>663</v>
+      </c>
+      <c r="F37" s="7">
+        <v>1133</v>
+      </c>
+      <c r="G37" s="7">
+        <v>11259</v>
+      </c>
+      <c r="H37" s="7">
+        <v>399</v>
+      </c>
+      <c r="I37" s="7">
+        <v>365</v>
+      </c>
+      <c r="J37" s="7">
+        <v>955</v>
+      </c>
+      <c r="K37" s="7">
+        <v>3233</v>
+      </c>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
         <v>2024</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="11">
         <v>27485</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="6">
         <v>3797</v>
       </c>
-      <c r="D38" s="1"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D38" s="7">
+        <v>127</v>
+      </c>
+      <c r="E38" s="7">
+        <v>223</v>
+      </c>
+      <c r="F38" s="7">
+        <v>1860</v>
+      </c>
+      <c r="G38" s="7">
+        <v>19906</v>
+      </c>
+      <c r="H38" s="7">
+        <v>726</v>
+      </c>
+      <c r="I38" s="7">
+        <v>734</v>
+      </c>
+      <c r="J38" s="7">
+        <v>1084</v>
+      </c>
+      <c r="K38" s="7">
+        <v>6622</v>
+      </c>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
